--- a/March_Release_DBS/Cypress/fixtures/StaffTemplate.xlsx
+++ b/March_Release_DBS/Cypress/fixtures/StaffTemplate.xlsx
@@ -430,28 +430,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PP1237</v>
+        <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>helponesa</v>
+        <v>PP$#@37</v>
       </c>
       <c r="C2" t="str">
-        <v>testpsa</v>
+        <v>Jolie</v>
       </c>
       <c r="D2" t="str">
-        <v>dbsteststaff0788@yopmail.com</v>
+        <v>Swift</v>
       </c>
       <c r="E2" t="str">
-        <v>3245320049</v>
+        <v>jolie@yopmail.com</v>
       </c>
       <c r="F2" t="str">
-        <v>3245320049</v>
+        <v>2884493194</v>
       </c>
       <c r="G2" t="str">
-        <v>Collections Manager</v>
+        <v>Audit and Risk</v>
       </c>
       <c r="H2" t="str">
-        <v>BANGALORE</v>
+        <v>Audit Manager</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Bangalore</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_DBS/Cypress/fixtures/StaffTemplate.xlsx
+++ b/March_Release_DBS/Cypress/fixtures/StaffTemplate.xlsx
@@ -430,28 +430,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Telecaller</v>
+        <v>Others</v>
       </c>
       <c r="B2" t="str">
-        <v>PP$#@37</v>
+        <v>77261</v>
       </c>
       <c r="C2" t="str">
-        <v>Jolie</v>
+        <v>Jamar</v>
       </c>
       <c r="D2" t="str">
-        <v>Swift</v>
+        <v>Tromp-Ziemann</v>
       </c>
       <c r="E2" t="str">
-        <v>jolie@yopmail.com</v>
+        <v>jamar@yopmail.com</v>
       </c>
       <c r="F2" t="str">
-        <v>2884493194</v>
+        <v>6346638557</v>
       </c>
       <c r="G2" t="str">
-        <v>Audit and Risk</v>
+        <v>Collection Staff Frontend</v>
       </c>
       <c r="H2" t="str">
-        <v>Audit Manager</v>
+        <v>DBS Telecaller</v>
       </c>
       <c r="I2" t="str">
         <v>Bangalore</v>
